--- a/bench/data/files/synthetic8_C.xlsx
+++ b/bench/data/files/synthetic8_C.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Capital</t>
+          <t>Drift Corp</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -594,35 +594,35 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2012-10-27</t>
+          <t>2013-05-01</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>987.8</v>
+        <v>983.3</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1848.2</v>
+        <v>1854.6</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>120.2</v>
+        <v>145.8</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>122.1</v>
+        <v>180.7</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>248.3</v>
+        <v>443.2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.67</v>
+        <v>0.751</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Emma Mueller; Amanda Williams; Olivia Williams; Wei Chen; Jennifer Fischer</t>
+          <t>Elena Xu; Thomas Xu</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -634,17 +634,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Echo Solutions</t>
+          <t>Atlas Solutions</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -654,35 +654,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2012-11-03</t>
+          <t>2010-06-21</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2014-07-31</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1916.9</v>
+        <v>1424.6</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3988.9</v>
+        <v>1374.7</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>216.6</v>
+        <v>196.8</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>504.1</v>
+        <v>418.3</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>851.2</v>
+        <v>339.8</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.608</v>
+        <v>0.156</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Matthew O'Brien; Sarah Evans; Rachel Gupta; Sophie Ivanov; Matthew Chen</t>
+          <t>James Evans; Laura Evans</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -694,17 +694,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Vertex Bio</t>
+          <t>Cipher Dynamics</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -714,35 +714,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2013-05-05</t>
+          <t>2013-09-09</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
+          <t>2016-08-25</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>199.4</v>
+        <v>1185.1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>609.7</v>
+        <v>1110.9</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>52.8</v>
+        <v>215.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>79.3</v>
+        <v>382.8</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>45.7</v>
+        <v>150.6</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.248</v>
+        <v>0.163</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Michael Evans; Ahmed Xu; David Evans; Thomas O'Brien</t>
+          <t>Yuki Vega; Sarah Patel; Yuki Vega</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -754,17 +754,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Echo AG</t>
+          <t>Lattice Corp</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -774,31 +774,31 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010-07-27</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
-        <v>1744</v>
+        <v>1163.4</v>
       </c>
       <c r="H8" s="4" t="n">
         <v/>
       </c>
       <c r="I8" s="4" t="n">
-        <v>409.3</v>
+        <v>162.2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v/>
       </c>
       <c r="K8" s="4" t="n">
-        <v>234.2</v>
+        <v>337.2</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.33</v>
+        <v>0.428</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Michael Brown; Sarah Williams; Yuki Gupta; Priya Zhang</t>
+          <t>Matthew Patel; Ravi Patel; Ravi Davis</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -810,17 +810,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Echo Networks</t>
+          <t>Zenith Holdings</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -830,35 +830,35 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2012-11-14</t>
+          <t>2013-12-21</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>749.5</v>
+        <v>1995.6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1151</v>
+        <v>3240</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>203.3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>106.8</v>
+        <v>398.6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>174.4</v>
+        <v>557.4</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.792</v>
+        <v>0.535</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Lopez; Hannah Zhang</t>
+          <t>Jessica Tanaka; Sophie Johnson; Emma Xu; Jessica Chen; Priya Hassan</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Krypton Industries</t>
+          <t>Zenith Logic</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -890,35 +890,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2010-02-06</t>
+          <t>2012-08-21</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2018-09-16</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1945.1</v>
+        <v>589.2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3532.6</v>
+        <v>1502.4</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>254.2</v>
+        <v>114.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>341.7</v>
+        <v>118.7</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>311.2</v>
+        <v>65.7</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.525</v>
+        <v>0.896</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Wei Hassan; Robert Schmidt; Jessica Schmidt; Jennifer Zhang</t>
+          <t>Andrew Johnson; Daniel Lopez</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -930,7 +930,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Drift Industries</t>
+          <t>Tessera Energy</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -950,35 +950,35 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2012-12-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2020-10-31</t>
+          <t>2016-02-11</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1282.6</v>
+        <v>1633.5</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1300</v>
+        <v>4671.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>230.3</v>
+        <v>307.4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>410.2</v>
+        <v>337.4</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>496.3</v>
+        <v>1092.4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.759</v>
+        <v>0.773</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Robert Nakamura; Priya Brown; Jennifer Davis</t>
+          <t>Matthew Patel; Laura Johnson; Ravi Ueno; Olivia Fischer; Thomas Hassan</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Zenith Health</t>
+          <t>Xenith Ltd</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1010,35 +1010,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2012-03-15</t>
+          <t>2011-11-20</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2018-03-13</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>304.2</v>
+        <v>788.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>622.5</v>
+        <v>1478.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>44.8</v>
+        <v>153.4</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>54.2</v>
+        <v>124.5</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>61.2</v>
+        <v>125.4</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.337</v>
+        <v>0.624</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Wei Brown; Robert Vega; Laura Gupta; Thomas Williams; Ravi Patel</t>
+          <t>Jessica Tanaka; Daniel Hassan</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1050,17 +1050,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Helix Tech</t>
+          <t>Lumen Systems</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1070,35 +1070,35 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2013-09-25</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
+          <t>2016-06-27</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>124.7</v>
+        <v>914.5</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>298.8</v>
+        <v>1200.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20.4</v>
+        <v>255.3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>856</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.922</v>
+        <v>0.432</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Ravi Tanaka; Amanda Xu; Thomas Rossi</t>
+          <t>Ravi Xu; Christopher Evans</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1108,139 +1108,41 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Vertex Pharma</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2010-07-12</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2014-05-19</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1086.4</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1692</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>288.7</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>601</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>429.9</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>Mark Brown; Sarah Fischer</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>Fund I</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Apex Holdings</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2010-08-12</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>2013-05-29</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>975</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>2270.2</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>200.2</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>171</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>525.7</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>Laura Nakamura; Mark Johnson; Yuki Zhang; David Fischer</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>Fund I</t>
-        </is>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Fund I Average</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1186.4</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2054.1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>440.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nova Bio</t>
+          <t>Forge Energy</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1250,47 +1152,47 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2010-05-05</t>
+          <t>2015-02-10</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2018-03-09</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1560.1</v>
+        <v>922.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1362.3</v>
+        <v>2609.5</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>423.8</v>
+        <v>154.7</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>510.4</v>
+        <v>356.7</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>613.8</v>
+        <v>463.8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.75</v>
+        <v>0.893</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Sophie Schmidt; Robert Hassan; Jennifer Rossi</t>
+          <t>Christopher Zhang; Robert Hassan; Rachel Yamamoto</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Logistics</t>
+          <t>Polaris Health</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1300,53 +1202,57 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2011-05-15</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>2014-12-16</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-07</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
-        <v>333.9</v>
+        <v>477</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v/>
+        <v>1222.3</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>79.8</v>
+        <v>48.8</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v/>
+        <v>107.2</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>334.2</v>
+        <v>180.8</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.609</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Sarah Davis; Sarah Johnson; Jennifer Lopez; Christopher Anderson; Wei Kim</t>
+          <t>Jennifer Ivanov; Michael Hassan; Hannah Lopez</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Vertex Solutions</t>
+          <t>Xenith AG</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1356,7 +1262,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1366,79 +1272,177 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2011-03-20</t>
+          <t>2014-03-08</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2014-12-29</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>581.2</v>
+        <v>445.6</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1456.2</v>
+        <v>461.6</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>132.3</v>
+        <v>68.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>229.2</v>
+        <v>138.5</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>257.4</v>
+        <v>100.5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.885</v>
+        <v>0.225</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Mark Patel; James Lopez</t>
+          <t>Yuki Xu; Matthew Zhang</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Fund I Average</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>985.1</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1677.7</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>263.1</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>333.9</v>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Meridian Dynamics</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>2013-03-18</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>2021-02-03</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>899.7</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1418.3</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>David Mueller; Yuki Brown; Sophie Patel; Emma Schmidt</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Fund II</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Lumen Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2015-11-10</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>856.4</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1740.2</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>685.3</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Gupta; David Fischer; Michael Ueno; Olivia Hassan; Wei Johnson</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Fund II</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Cipher Capital</t>
+          <t>Quanta Foods</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1448,35 +1452,35 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2012-12-16</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1560.2</v>
+        <v>202.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3991.2</v>
+        <v>636.9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>420.8</v>
+        <v>47.2</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>546.2</v>
+        <v>69</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>534</v>
+        <v>34.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.892</v>
+        <v>0.676</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Laura Tanaka; Priya O'Brien; Sophie Xu; Olivia O'Brien; Mark Brown</t>
+          <t>Thomas Chen; Thomas Rossi; Sophie Johnson</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1488,17 +1492,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Glacier Corp</t>
+          <t>Cobalt SA</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1508,35 +1512,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2012-05-08</t>
+          <t>2015-10-23</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>273.7</v>
+        <v>1214.1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>583.5</v>
+        <v>2758.5</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>39.8</v>
+        <v>180.7</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>32</v>
+        <v>367.1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>754.1</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.651</v>
+        <v>0.389</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>David Davis; David Anderson; Thomas Tanaka</t>
+          <t>Christopher Qureshi; Sophie Yamamoto; Priya Williams</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1546,139 +1550,41 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Quanta Logistics</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Boston, MA</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>2012-09-04</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>2017-11-06</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>643.6</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>1633.8</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>303.7</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Amanda Williams; Emma Lopez</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>Fund II</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Radial Partners</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-16</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>2018-10-19</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>899.7</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>1288.5</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>145.4</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>338</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>401</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Robert Brown; Olivia Vega; Yuki Vega</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>Fund II</t>
-        </is>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Fund II Average</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>716.9</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1549.6</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>354.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Beacon Energy</t>
+          <t>Echo GmbH</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1688,57 +1594,57 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2016-01-24</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1485.3</v>
+        <v>1177.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4984.9</v>
+        <v>2712.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>189.4</v>
+        <v>279.7</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>292.2</v>
+        <v>352.7</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>658.5</v>
+        <v>689.6</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.569</v>
+        <v>0.391</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Emma Chen; Sarah Ueno</t>
+          <t>Sophie Yamamoto; Elena Williams</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Forge Media</t>
+          <t>Halo Pharma</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1748,57 +1654,57 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2012-12-08</t>
+          <t>2017-05-14</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1521.4</v>
+        <v>1271.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1665.6</v>
+        <v>1016</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>145.9</v>
+        <v>320.5</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>236.6</v>
+        <v>782.2</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>360.2</v>
+        <v>1081.7</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.995</v>
+        <v>0.865</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Matthew Gupta; Sarah Nakamura; Laura Williams; Hannah Fischer</t>
+          <t>Hannah Davis; Matthew Vega; James Lopez; Daniel Kim; Ahmed Zhang</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Helix Group</t>
+          <t>Radial SA</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1808,57 +1714,57 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2013-03-03</t>
+          <t>2016-11-15</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1631.7</v>
+        <v>630.5</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2858.2</v>
+        <v>739.7</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>218.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>234.6</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>619</v>
+        <v>361.7</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.359</v>
+        <v>0.773</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>James Brown; Sarah Qureshi</t>
+          <t>Daniel Anderson; Wei Evans; Jennifer Zhang; David Rossi</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Wavelength GmbH</t>
+          <t>Gravity Media</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1868,69 +1774,167 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2012-10-01</t>
+          <t>2017-10-20</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1856.1</v>
+        <v>1615.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3142.1</v>
+        <v>1967.1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>299.2</v>
+        <v>198.4</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>265.7</v>
+        <v>171.9</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>213.6</v>
+        <v>877.6</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.829</v>
+        <v>0.213</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Matthew O'Brien; James Qureshi; Thomas Gupta</t>
+          <t>Priya Xu; Daniel Xu; Sophie Johnson; Thomas Mueller</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Fund II Average</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>1234</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>2518.5</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>193.9</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>252.5</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>395.1</v>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Nimbus Dynamics</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2018-07-02</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1008.3</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>2151</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Ravi Brown; Daniel Tanaka; Andrew Williams; Matthew Vega; James Schmidt</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Fund III</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Lattice Group</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1956.2</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>4361.9</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>525.5</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>844.5</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>1773.3</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Ahmed Lopez; Sarah Chen; Matthew Hassan</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Fund III</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Gravity Dynamics</t>
+          <t>Kepler Industries</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1940,7 +1944,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1950,35 +1954,35 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2014-12-27</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>449.4</v>
+        <v>72.8</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>949.3</v>
+        <v>112.8</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>88</v>
+        <v>10.6</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>80.3</v>
+        <v>15.4</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>377.4</v>
+        <v>42.2</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.526</v>
+        <v>0.598</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Elena Xu; Christopher Zhang; Matthew Evans; Yuki Johnson</t>
+          <t>David Xu; Hannah Anderson</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -1988,129 +1992,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Zenith Capital</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Paris, FR</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>2016-02-04</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1410</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>3023</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>405.2</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>820.7</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>James Yamamoto; Laura Lopez; Matthew Evans; Sarah O'Brien; Ravi Williams</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Cipher Media</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>489.7</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>780.5</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>477.2</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Rachel Rossi; Olivia Johnson</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Fund III Average</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1104.7</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1865.8</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>703.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Apex SA</t>
+          <t>Umbra Networks</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2120,67 +2026,63 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2014-05-04</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2020-06-09</t>
-        </is>
-      </c>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
-        <v>736.9</v>
+        <v>781.2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1484.3</v>
+        <v/>
       </c>
       <c r="I34" s="4" t="n">
-        <v>140</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>207.7</v>
+        <v/>
       </c>
       <c r="K34" s="4" t="n">
-        <v>623.6</v>
+        <v>248.4</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.758</v>
+        <v>0.539</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>David Patel; Ahmed Rossi</t>
+          <t>Sophie Brown; Jessica Tanaka; David Hassan</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Echo Corp</t>
+          <t>Helix Inc</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2190,52 +2092,52 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1606.6</v>
+        <v>696.7</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1651.6</v>
+        <v>1188.3</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>247.4</v>
+        <v>128.1</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>416.2</v>
+        <v>159.7</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>628.3</v>
+        <v>571.6</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Sophie Evans; Andrew Evans</t>
+          <t>Jessica Gupta; Amanda Anderson; Ravi O'Brien</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Yields Capital</t>
+          <t>Ember Bio</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2250,79 +2152,177 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1814.3</v>
+        <v>455.4</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>3563.9</v>
+        <v>959.7</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>402.9</v>
+        <v>91.5</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>865.4</v>
+        <v>116.3</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1709.8</v>
+        <v>49.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.659</v>
+        <v>0.223</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Olivia Hassan; Laura Yamamoto</t>
+          <t>Matthew Ueno; Amanda O'Brien; Jessica Fischer</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Fund III Average</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>1084.5</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1908.8</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>194.7</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>349.8</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>772.8</v>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Helix AG</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2019-07-12</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1782.4</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>2972.1</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>853.8</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>1568.4</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Ahmed Ueno; Andrew Nakamura; Emma Fischer; Wei Xu</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Polaris Inc</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2018-12-22</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1205.1</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1879.8</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>878.4</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Hassan; Michael Yamamoto; Thomas Kim; David Evans; Olivia Williams</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Lattice Industries</t>
+          <t>Cipher Materials</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2332,35 +2332,35 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2019-03-06</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>508.6</v>
+        <v>144.2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1429.5</v>
+        <v>351.7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>140.3</v>
+        <v>39.6</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>320.5</v>
+        <v>54.3</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>447</v>
+        <v>149</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.531</v>
+        <v>0.835</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>David Hassan; Thomas Rossi; Jessica Fischer; Thomas Xu</t>
+          <t>Ravi Evans; Ahmed Anderson; Olivia Mueller; Sophie Chen; Andrew Davis</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Lattice Bio</t>
+          <t>Zenith Inc</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2392,35 +2392,35 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2017-05-16</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1159.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>3834.4</v>
+        <v>155.4</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>288.6</v>
+        <v>5.6</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>447.2</v>
+        <v>10</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>546.2</v>
+        <v>5.8</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.884</v>
+        <v>0.351</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Elena Anderson; Emma Schmidt; Emma Kim; Mark Vega</t>
+          <t>Sarah Ueno; Jessica Kim; Laura Vega</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2432,17 +2432,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Quanta SA</t>
+          <t>Orion Bio</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2452,35 +2452,35 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2018-02-22</t>
+          <t>2016-04-13</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>217.1</v>
+        <v>303.2</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>570.3</v>
+        <v>908.1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>55.8</v>
+        <v>53.6</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>131.7</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>211.3</v>
+        <v>230.8</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.408</v>
+        <v>0.87</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Jessica Kim; Ravi Hassan; Elena Kim; Andrew Mueller; Hannah O'Brien</t>
+          <t>Jennifer Ueno; Thomas Schmidt</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2490,129 +2490,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Cipher Networks</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>2016-10-04</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>1731.2</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>5890.9</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>306.1</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>321.2</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>440.4</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>James Lopez; Rachel Lopez; Thomas Hassan; Sophie Fischer; Thomas Qureshi</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>Fund IV</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Gravity Capital</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Boston, MA</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>2018-06-03</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>1585.6</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>4543.1</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>270.8</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>420.7</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>409.7</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>Laura Vega; Sophie Williams; Jennifer Chen; Amanda Patel; Hannah Hassan</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>Fund IV</t>
-        </is>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Fund IV Average</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>679.4</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>1202.2</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>283.2</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>462.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Forge Networks</t>
+          <t>Yields SA</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2622,7 +2524,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2632,57 +2534,57 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2016-05-27</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2019-05-17</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1963.2</v>
+        <v>932.3</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1517.9</v>
+        <v>1568.6</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>400.1</v>
+        <v>202.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>948.9</v>
+        <v>184.5</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1649.7</v>
+        <v>624.3</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.592</v>
+        <v>0.979</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Mark Chen; Andrew Xu; Christopher Zhang; Sarah Rossi; Mark Ivanov</t>
+          <t>Jennifer Johnson; James Davis</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Halo Foods</t>
+          <t>Krypton Systems</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2692,57 +2594,57 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2016-03-21</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>548.6</v>
+        <v>1442.7</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>701.5</v>
+        <v>3021.9</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>51.2</v>
+        <v>138.6</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>85.5</v>
+        <v>297.1</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>155.7</v>
+        <v>458.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.715</v>
+        <v>0.254</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Christopher O'Brien; James Evans; Amanda Hassan</t>
+          <t>Emma Kim; Mark Anderson; Wei Yamamoto</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Lumen Ltd</t>
+          <t>Halo Logic</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2752,57 +2654,57 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2019-10-16</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1952.4</v>
+        <v>1847.5</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>6104</v>
+        <v>5778.2</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>215.9</v>
+        <v>504.2</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>244.8</v>
+        <v>481.2</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>410.5</v>
+        <v>1386.8</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Rachel Anderson; Amanda Lopez; David Gupta</t>
+          <t>Daniel Yamamoto; Andrew Ueno; Sarah Patel; Andrew Davis; Priya Fischer</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Vertex Industries</t>
+          <t>Junction Tech</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2812,57 +2714,57 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1748.6</v>
+        <v>747.4</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3602.7</v>
+        <v>1541.4</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>456.8</v>
+        <v>62.3</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>649.6</v>
+        <v>55.8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1751.6</v>
+        <v>56.5</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.338</v>
+        <v>0.196</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Rachel Johnson; Thomas Lopez; Mark Schmidt</t>
+          <t>Sophie Hassan; Yuki Fischer; Olivia Hassan; Sarah Mueller</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Radial Materials</t>
+          <t>Ember Inc</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2872,69 +2774,163 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1429</v>
+        <v>1453.9</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1465.4</v>
+        <v>1624.1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>178.2</v>
+        <v>303</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>286.1</v>
+        <v>678.8</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>481.2</v>
+        <v>1344.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.614</v>
+        <v>0.496</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Emma Mueller; Rachel Ueno</t>
+          <t>Mark Zhang; Emma Williams</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Fund IV Average</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>1284.4</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>2966</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>379.4</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>650.3</v>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Vertex Materials</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>2020-04-17</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>530.8</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Davis; David Patel; Elena Tanaka; Yuki Qureshi</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Meridian AG</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2018-07-17</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="n">
+        <v>484.5</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>369.8</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Emma Chen; Olivia Nakamura; Elena Fischer; Robert Gupta; Olivia Zhang</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Junction Networks</t>
+          <t>Glacier Group</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -2944,7 +2940,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2954,35 +2950,35 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2018-09-28</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1375.1</v>
+        <v>1219.6</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1452.8</v>
+        <v>1173.6</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>331.6</v>
+        <v>250.8</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>329.1</v>
+        <v>230.3</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1011.8</v>
+        <v>153.8</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>0.394</v>
+        <v>0.544</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>David Schmidt; Michael Tanaka; Mark Patel; Sarah Mueller; James Vega</t>
+          <t>Mark Hassan; Sarah Ivanov; Elena O'Brien; Amanda Johnson</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -2994,17 +2990,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Labs</t>
+          <t>Beacon Inc</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3014,35 +3010,35 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2019-05-14</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>152.3</v>
+        <v>1157.6</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>114.3</v>
+        <v>2441.9</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>33.1</v>
+        <v>222</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>40.3</v>
+        <v>296.6</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>133.8</v>
+        <v>894.1</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.524</v>
+        <v>0.196</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Rachel Patel; Jennifer Zhang; Elena O'Brien; Elena Nakamura; Wei Tanaka</t>
+          <t>Robert Tanaka; Yuki Nakamura; Sarah Qureshi; Matthew Tanaka</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -3054,7 +3050,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Radial Foods</t>
+          <t>Wavelength Logic</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3064,7 +3060,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3074,35 +3070,35 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2020-04-17</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>193.6</v>
+        <v>1016.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>228.4</v>
+        <v>1392.1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>34.6</v>
+        <v>208.5</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>45.4</v>
+        <v>413.8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>47.5</v>
+        <v>246.9</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Andrew Davis; Daniel O'Brien; Wei Brown</t>
+          <t>Olivia Nakamura; Daniel Ueno; Sophie Evans</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -3114,17 +3110,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Drift AG</t>
+          <t>Halo Solutions</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3134,35 +3130,35 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2020-04-19</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>684.2</v>
+        <v>479.9</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1888.2</v>
+        <v>1327.6</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>153.4</v>
+        <v>60.3</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>121.8</v>
+        <v>190.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.855</v>
+        <v>0.639</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Andrew Xu; Amanda Mueller</t>
+          <t>Michael Evans; Robert Rossi; Amanda Evans; Yuki Schmidt</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -3172,101 +3168,191 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Fund V Average</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>601.3</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>920.9</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>328.7</v>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Nova Solutions</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>2019-07-22</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>1779</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>2732.8</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>364.8</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>Robert Schmidt; Ravi Davis; James Lopez; Michael Schmidt; Sarah Davis</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Forge Solutions</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>2019-02-25</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>Laura Anderson; Ahmed Yamamoto</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Stratus Group</t>
+          <t>Lumen Partners</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2021-10-16</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
+          <t>2018-03-24</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
-        <v>184</v>
+        <v>1413.9</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>228</v>
+        <v/>
       </c>
       <c r="I57" s="4" t="n">
-        <v>28.1</v>
+        <v>188.6</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>27.7</v>
+        <v/>
       </c>
       <c r="K57" s="4" t="n">
-        <v>66.3</v>
+        <v>668.6</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.666</v>
+        <v>0.436</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Sophie Williams; Ravi Zhang</t>
+          <t>Jessica Evans; Amanda Zhang; Amanda Tanaka; Daniel O'Brien; Thomas Ivanov</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>Fund VI</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Iris Health</t>
+          <t>Wavelength Bio</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3276,173 +3362,75 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2018-12-26</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
-        <v>1060.5</v>
+        <v>939.2</v>
       </c>
       <c r="H58" s="4" t="n">
         <v/>
       </c>
       <c r="I58" s="4" t="n">
-        <v>143.4</v>
+        <v>253.4</v>
       </c>
       <c r="J58" s="4" t="n">
         <v/>
       </c>
       <c r="K58" s="4" t="n">
-        <v>598.5</v>
+        <v>151.1</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.821</v>
+        <v>0.298</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Robert Johnson; Elena Lopez</t>
+          <t>Andrew Lopez; Andrew Chen; Jennifer O'Brien; Ravi Evans</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Fund VI</t>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Lumen Group</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>2020-04-13</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>Daniel Fischer; Sophie Kim; Jessica Xu; Daniel Qureshi; Wei Johnson</t>
-        </is>
-      </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>Fund VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Glacier Systems</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Sydney, AU</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-12</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>2023-03-12</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>1008.3</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>2712.1</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>212.2</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>191.4</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>280.8</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="M60" s="4" t="inlineStr">
-        <is>
-          <t>Yuki Tanaka; Olivia Anderson; Jennifer Qureshi; Michael Brown</t>
-        </is>
-      </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>Fund VI</t>
-        </is>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Fund V Average</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>1017.9</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>290.9</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>493.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Fathom Corp</t>
+          <t>Ember Solutions</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3452,35 +3440,35 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1064.3</v>
+        <v>1586.8</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1993.2</v>
+        <v>4272.1</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>115.2</v>
+        <v>327.7</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>169.8</v>
+        <v>453.1</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>174.9</v>
+        <v>302.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0.532</v>
+        <v>0.457</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Laura Nakamura; Mark Anderson; Laura Williams; Laura Gupta</t>
+          <t>Michael Kim; Jennifer Lopez</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -3492,7 +3480,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Kepler SA</t>
+          <t>Xenith Systems</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -3502,45 +3490,41 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
-        <v>431.3</v>
+        <v>237.1</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>488.7</v>
+        <v/>
       </c>
       <c r="I62" s="4" t="n">
-        <v>49.3</v>
+        <v>59.3</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>43</v>
+        <v/>
       </c>
       <c r="K62" s="4" t="n">
-        <v>68.7</v>
+        <v>256.4</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.195</v>
+        <v>0.874</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>James Kim; Laura Gupta</t>
+          <t>Thomas Patel; Hannah Gupta; Olivia Hassan; James Nakamura</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -3552,17 +3536,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Vertex Group</t>
+          <t>Stratus Pharma</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3572,31 +3556,31 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
+          <t>2022-02-06</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
-        <v>397.7</v>
+        <v>186.4</v>
       </c>
       <c r="H63" s="4" t="n">
         <v/>
       </c>
       <c r="I63" s="4" t="n">
-        <v>66</v>
+        <v>22.4</v>
       </c>
       <c r="J63" s="4" t="n">
         <v/>
       </c>
       <c r="K63" s="4" t="n">
-        <v>246.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>0.458</v>
+        <v>0.589</v>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>James Nakamura; Yuki Hassan</t>
+          <t>Jessica Zhang; Jessica Chen; Laura O'Brien; Jessica Kim; James Johnson</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -3608,55 +3592,51 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Indigo Group</t>
+          <t>Polaris Systems</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>2023-12-23</t>
-        </is>
-      </c>
+          <t>2023-11-06</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
-        <v>1336.2</v>
+        <v>1765.8</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>3420.6</v>
+        <v/>
       </c>
       <c r="I64" s="4" t="n">
-        <v>260.6</v>
+        <v>146.8</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>281.7</v>
+        <v/>
       </c>
       <c r="K64" s="4" t="n">
-        <v>655.2</v>
+        <v>356</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.622</v>
+        <v>0.798</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Sarah Hassan; Emma Yamamoto; Robert Evans</t>
+          <t>Jessica Vega; Hannah Rossi; Yuki Schmidt</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -3668,17 +3648,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Fathom Logistics</t>
+          <t>Beacon AG</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3688,31 +3668,31 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
-        <v>1555.9</v>
+        <v>1354.6</v>
       </c>
       <c r="H65" s="4" t="n">
         <v/>
       </c>
       <c r="I65" s="4" t="n">
-        <v>158.7</v>
+        <v>304.1</v>
       </c>
       <c r="J65" s="4" t="n">
         <v/>
       </c>
       <c r="K65" s="4" t="n">
-        <v>374.5</v>
+        <v>541.5</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>0.256</v>
+        <v>0.915</v>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>Sophie Yamamoto; Amanda Anderson</t>
+          <t>Daniel Williams; Hannah Yamamoto; Michael Zhang</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -3722,101 +3702,101 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Nimbus Networks</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>1844.5</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>6028.1</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>284.3</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Schmidt; Mark Lopez; Elena Schmidt; Amanda Chen</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Fund VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Fund VI Average</t>
         </is>
       </c>
-      <c r="G66" s="6" t="n">
-        <v>789.3</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>1493</v>
-      </c>
-      <c r="I66" s="6" t="n">
-        <v>116.1</v>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>123.8</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>278.1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Xenith Energy</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>1154.3</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>1375</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>217</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>213.7</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>323.3</v>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
-        <is>
-          <t>David Qureshi; Elena Tanaka</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="inlineStr">
-        <is>
-          <t>Fund VII</t>
-        </is>
+      <c r="G67" s="6" t="n">
+        <v>1162.5</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>5150.1</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>343.3</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>353.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Delta Logic</t>
+          <t>Nimbus Corp</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3826,31 +3806,31 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
-        <v>1063.5</v>
+        <v>1067.7</v>
       </c>
       <c r="H69" s="4" t="n">
         <v/>
       </c>
       <c r="I69" s="4" t="n">
-        <v>108.7</v>
+        <v>273</v>
       </c>
       <c r="J69" s="4" t="n">
         <v/>
       </c>
       <c r="K69" s="4" t="n">
-        <v>176.8</v>
+        <v>1103.3</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>0.887</v>
+        <v>0.517</v>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>Amanda Qureshi; Jessica Kim; Daniel Rossi</t>
+          <t>Robert Evans; Mark Ueno</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -3862,17 +3842,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Capital</t>
+          <t>Yields AG</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3882,35 +3862,35 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>252.6</v>
+        <v>1289.4</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>858.2</v>
+        <v>2850.1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>63</v>
+        <v>185.9</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>247</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>210.5</v>
+        <v>786.9</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.593</v>
+        <v>0.526</v>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>Matthew Brown; David Chen; Emma Kim</t>
+          <t>Ahmed Mueller; Andrew Davis; Christopher Yamamoto</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -3922,7 +3902,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Stratus Dynamics</t>
+          <t>Quanta Logistics</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3932,7 +3912,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3942,35 +3922,35 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1038</v>
+        <v>1015.2</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1422.8</v>
+        <v>1694.7</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>83.7</v>
+        <v>242.1</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>148.8</v>
+        <v>416.8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>269.1</v>
+        <v>209.4</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>0.541</v>
+        <v>0.369</v>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>Rachel Ivanov; Hannah Yamamoto; Yuki Tanaka; Michael Hassan; David Ivanov</t>
+          <t>Robert Xu; Yuki Vega; Sophie Fischer; Thomas Lopez</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -3982,51 +3962,55 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Ember Industries</t>
+          <t>Lumen Inc</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr"/>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
-        <v>918.3</v>
+        <v>667.4</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v/>
+        <v>1666.3</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>182.7</v>
+        <v>121</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v/>
+        <v>132.6</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>522.5</v>
+        <v>324</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.587</v>
+        <v>0.38</v>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Lopez; Daniel Tanaka; David Anderson</t>
+          <t>Rachel Ueno; Emma Fischer; David Gupta; Daniel Schmidt</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -4038,271 +4022,267 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Yields Solutions</t>
+          <t>Echo Solutions</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>816</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>1741.5</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>Christopher Davis; Mark Rossi; Amanda Patel; Hannah Rossi; Christopher Vega</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>Fund VII</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Nimbus Bio</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
           <t>Unrealized</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="n">
-        <v>1466.6</v>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>172.4</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>535.4</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M73" s="4" t="inlineStr">
-        <is>
-          <t>Yuki Williams; Daniel Chen; Laura Brown; David Fischer</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="n">
+        <v>1984.1</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>445.6</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>1783.3</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>Priya Tanaka; Jennifer Tanaka; Amanda Johnson</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>Fund VII</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Fund VII Average</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="n">
-        <v>982.2</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>1218.7</v>
-      </c>
-      <c r="I74" s="6" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>339.6</v>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Polaris Corp</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Toronto, CA</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>Elena Kim; Laura Fischer; Priya Evans; Daniel Gupta; Yuki Nakamura</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Fund VII</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Lumen AG</t>
+          <t>Wavelength Ltd</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
-        <v>458.4</v>
+        <v>249.3</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1388.7</v>
+        <v/>
       </c>
       <c r="I76" s="4" t="n">
-        <v>100.1</v>
+        <v>50.5</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>169.1</v>
+        <v/>
       </c>
       <c r="K76" s="4" t="n">
-        <v>395.4</v>
+        <v>146.1</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.979</v>
+        <v>0.823</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>Rachel Vega; Daniel Evans; Matthew Chen; Laura Nakamura; Hannah Fischer</t>
+          <t>Ahmed Vega; Thomas Brown</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>Fund VIII</t>
+          <t>Fund VII</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>Polaris Capital</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="n">
-        <v>945.4</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K77" s="4" t="n">
-        <v>514.6</v>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="M77" s="4" t="inlineStr">
-        <is>
-          <t>Sophie Vega; Andrew Mueller; Matthew Brown; Rachel Mueller; Yuki Hassan</t>
-        </is>
-      </c>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>Fund VIII</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Gravity Pharma</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-12</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>1941</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>5366.4</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>365.1</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>579.9</v>
-      </c>
-      <c r="K78" s="4" t="n">
-        <v>1055.1</v>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="M78" s="4" t="inlineStr">
-        <is>
-          <t>Ahmed Lopez; Mark Lopez; Laura Qureshi; Matthew Mueller</t>
-        </is>
-      </c>
-      <c r="N78" s="4" t="inlineStr">
-        <is>
-          <t>Fund VIII</t>
-        </is>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Fund VII Average</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>934</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>1988.2</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>292.9</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>587.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Pharma</t>
+          <t>Beacon Solutions</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4312,31 +4292,31 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
-        <v>116.1</v>
+        <v>1695.8</v>
       </c>
       <c r="H79" s="4" t="n">
         <v/>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21.7</v>
+        <v>237.4</v>
       </c>
       <c r="J79" s="4" t="n">
         <v/>
       </c>
       <c r="K79" s="4" t="n">
-        <v>14.1</v>
+        <v>663.3</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>Amanda Gupta; Yuki Qureshi</t>
+          <t>Wei Xu; Christopher Lopez</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -4348,17 +4328,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Krypton Holdings</t>
+          <t>Krypton SA</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4368,35 +4348,35 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>1078.2</v>
+        <v>1256.3</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>3220.7</v>
+        <v>2444.5</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>278.3</v>
+        <v>288.6</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>330.8</v>
+        <v>674.2</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>174.9</v>
+        <v>714.9</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.454</v>
+        <v>0.712</v>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>Michael Schmidt; Robert Ivanov</t>
+          <t>Wei Rossi; James Hassan; Michael Kim</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -4408,51 +4388,55 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Junction Solutions</t>
+          <t>Cipher Partners</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
-        <v>699.3</v>
+        <v>1325.6</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v/>
+        <v>3503.2</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>171.9</v>
+        <v>185</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v/>
+        <v>298.1</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>330.2</v>
+        <v>527.1</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.344</v>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>James O'Brien; Yuki Brown; Olivia Ueno</t>
+          <t>Elena Qureshi; Amanda Zhang</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -4464,7 +4448,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Krypton Capital</t>
+          <t>Atlas Group</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -4474,7 +4458,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4484,31 +4468,31 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
-        <v>473.1</v>
+        <v>935.3</v>
       </c>
       <c r="H82" s="4" t="n">
         <v/>
       </c>
       <c r="I82" s="4" t="n">
-        <v>89.3</v>
+        <v>183.8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v/>
       </c>
       <c r="K82" s="4" t="n">
-        <v>187.6</v>
+        <v>758.5</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.619</v>
+        <v>0.22</v>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>Elena Ivanov; Jennifer Ivanov</t>
+          <t>Amanda Nakamura; Sophie Fischer; David Hassan; Elena Xu; Hannah Patel</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -4520,17 +4504,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Lumen Foods</t>
+          <t>Quanta Capital</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4540,31 +4524,31 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2027-04-02</t>
+          <t>2027-11-27</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
-        <v>163.9</v>
+        <v>335</v>
       </c>
       <c r="H83" s="4" t="n">
         <v/>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20.3</v>
+        <v>41.8</v>
       </c>
       <c r="J83" s="4" t="n">
         <v/>
       </c>
       <c r="K83" s="4" t="n">
-        <v>36.7</v>
+        <v>153.5</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>0.877</v>
+        <v>0.5</v>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>Olivia Ueno; Sarah Johnson; Ravi Xu; Ahmed Brown; Mark Patel</t>
+          <t>Andrew Kim; Ahmed Anderson; Emma Davis; Ahmed Schmidt; Christopher Qureshi</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -4576,12 +4560,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Echo Media</t>
+          <t>Junction Holdings</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4591,40 +4575,36 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
-        <v>1963.9</v>
+        <v>702.2</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>6836.9</v>
+        <v/>
       </c>
       <c r="I84" s="4" t="n">
-        <v>505.4</v>
+        <v>140.8</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1159.9</v>
+        <v/>
       </c>
       <c r="K84" s="4" t="n">
-        <v>441.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.347</v>
+        <v>0.661</v>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>Elena Hassan; Hannah Brown; Christopher Anderson</t>
+          <t>Sarah O'Brien; Sarah Ivanov; Robert Johnson; Jennifer Lopez; Christopher Brown</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -4636,51 +4616,55 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Iris Ltd</t>
+          <t>Delta Networks</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr"/>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
-        <v>486</v>
+        <v>1290.4</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v/>
+        <v>3055.9</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>72.5</v>
+        <v>267.2</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v/>
+        <v>544.6</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>91.7</v>
+        <v>849.2</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>0.992</v>
+        <v>0.705</v>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>Michael Qureshi; Ahmed Ivanov; Laura Evans; Andrew Patel</t>
+          <t>Sarah Nakamura; Daniel Williams; Michael Kim; Sophie Chen; David Davis</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -4692,141 +4676,145 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Junction Group</t>
+          <t>Bloom Solutions</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>1181.1</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>3770.1</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>661.9</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>Michael Zhang; Jessica Williams; Ravi Hassan; Emma Patel; Andrew Chen</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>Fund VIII</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Stratus Labs</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Munich, DE</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
           <t>Unrealized</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="n">
-        <v>1145.5</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>316.9</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>1285.2</v>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="M86" s="4" t="inlineStr">
-        <is>
-          <t>Sarah Johnson; Wei Nakamura; Mark Kim; James Patel</t>
-        </is>
-      </c>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>Ahmed Davis; David Hassan; Laura Ivanov; Andrew Johnson</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
         <is>
           <t>Fund VIII</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>Fund VIII Average</t>
         </is>
       </c>
-      <c r="G87" s="6" t="n">
-        <v>861</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>4203.2</v>
-      </c>
-      <c r="I87" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>559.9</v>
-      </c>
-      <c r="K87" s="6" t="n">
-        <v>411.5</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Atlas Corp</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>2027-10-15</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="n">
-        <v>1499.5</v>
-      </c>
-      <c r="H89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>228.8</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K89" s="4" t="n">
-        <v>306.4</v>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="M89" s="4" t="inlineStr">
-        <is>
-          <t>Ravi Rossi; Ravi Rossi; Sarah Zhang; Robert Vega</t>
-        </is>
-      </c>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>Fund IX</t>
-        </is>
+      <c r="G88" s="6" t="n">
+        <v>987.6</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>3193.4</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>488.7</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>491.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Halo Group</t>
+          <t>Delta Foods</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -4836,7 +4824,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4846,31 +4834,31 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2028-12-05</t>
+          <t>2027-07-14</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
-        <v>116.7</v>
+        <v>562.4</v>
       </c>
       <c r="H90" s="4" t="n">
         <v/>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16.5</v>
+        <v>126.2</v>
       </c>
       <c r="J90" s="4" t="n">
         <v/>
       </c>
       <c r="K90" s="4" t="n">
-        <v>50</v>
+        <v>192.7</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0.889</v>
+        <v>0.95</v>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>James Hassan; Christopher Zhang</t>
+          <t>Ravi Fischer; Wei Rossi</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -4882,17 +4870,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Helix Ltd</t>
+          <t>Lattice Inc</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4902,31 +4890,31 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>2029-08-13</t>
+          <t>2027-12-07</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
-        <v>652.5</v>
+        <v>676</v>
       </c>
       <c r="H91" s="4" t="n">
         <v/>
       </c>
       <c r="I91" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>101.2</v>
       </c>
       <c r="J91" s="4" t="n">
         <v/>
       </c>
       <c r="K91" s="4" t="n">
-        <v>64.2</v>
+        <v>68</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>0.798</v>
+        <v>0.435</v>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>Priya Lopez; Elena Kim</t>
+          <t>Ahmed Ueno; Laura Schmidt; Elena Yamamoto; James Zhang</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -4938,7 +4926,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Orion Partners</t>
+          <t>Cobalt Solutions</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -4948,45 +4936,41 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2028-01-21</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
-        <v>396.1</v>
+        <v>1409.2</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>317.9</v>
+        <v/>
       </c>
       <c r="I92" s="4" t="n">
-        <v>51.4</v>
+        <v>188.6</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>114.1</v>
+        <v/>
       </c>
       <c r="K92" s="4" t="n">
-        <v>156.3</v>
+        <v>386.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.612</v>
+        <v>0.978</v>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>David Davis; Matthew Lopez; Ahmed Yamamoto; David Williams; Wei Hassan</t>
+          <t>Jessica Gupta; Hannah Nakamura</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -4998,12 +4982,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Umbra Foods</t>
+          <t>Ember Dynamics</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5018,31 +5002,31 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>2029-05-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
-        <v>1491.8</v>
+        <v>1956.7</v>
       </c>
       <c r="H93" s="4" t="n">
         <v/>
       </c>
       <c r="I93" s="4" t="n">
-        <v>252.7</v>
+        <v>225.9</v>
       </c>
       <c r="J93" s="4" t="n">
         <v/>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1060.9</v>
+        <v>989</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>0.528</v>
+        <v>0.923</v>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>Robert Mueller; Mark Johnson; Michael Nakamura; Jennifer Schmidt</t>
+          <t>Olivia Yamamoto; David Fischer</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -5054,12 +5038,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Fathom Labs</t>
+          <t>Ember GmbH</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5069,40 +5053,36 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
+          <t>2029-01-21</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
-        <v>1444.6</v>
+        <v>1778.9</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>2505.2</v>
+        <v/>
       </c>
       <c r="I94" s="4" t="n">
-        <v>166.7</v>
+        <v>494.4</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>381.1</v>
+        <v/>
       </c>
       <c r="K94" s="4" t="n">
-        <v>571.9</v>
+        <v>1979.9</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.51</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>Jennifer O'Brien; Hannah Johnson; Daniel Ivanov</t>
+          <t>Priya Patel; Jennifer Davis; Jennifer Hassan</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -5114,17 +5094,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Forge Materials</t>
+          <t>Krypton Corp</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5134,31 +5114,31 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2028-03-24</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
-        <v>374.3</v>
+        <v>1814.9</v>
       </c>
       <c r="H95" s="4" t="n">
         <v/>
       </c>
       <c r="I95" s="4" t="n">
-        <v>45.8</v>
+        <v>317.5</v>
       </c>
       <c r="J95" s="4" t="n">
         <v/>
       </c>
       <c r="K95" s="4" t="n">
-        <v>148.8</v>
+        <v>575.4</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>0.353</v>
+        <v>0.437</v>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>Olivia Ivanov; Rachel Ueno; David Gupta; Yuki Qureshi</t>
+          <t>Emma Johnson; Mark Nakamura; Christopher Schmidt</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -5170,17 +5150,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Kepler Dynamics</t>
+          <t>Atlas Inc</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5190,31 +5170,31 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2029-10-24</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
-        <v>178.2</v>
+        <v>944</v>
       </c>
       <c r="H96" s="4" t="n">
         <v/>
       </c>
       <c r="I96" s="4" t="n">
-        <v>31.9</v>
+        <v>241.1</v>
       </c>
       <c r="J96" s="4" t="n">
         <v/>
       </c>
       <c r="K96" s="4" t="n">
-        <v>123.2</v>
+        <v>873.5</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.251</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>Thomas Vega; Yuki Nakamura; Michael Chen; Matthew Chen</t>
+          <t>Matthew O'Brien; Sarah Gupta; Rachel Williams</t>
         </is>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -5226,17 +5206,17 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Delta Group</t>
+          <t>Lumen AG</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -5246,31 +5226,31 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>2027-08-12</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
-        <v>1030.6</v>
+        <v>1816.6</v>
       </c>
       <c r="H97" s="4" t="n">
         <v/>
       </c>
       <c r="I97" s="4" t="n">
-        <v>266.1</v>
+        <v>199.1</v>
       </c>
       <c r="J97" s="4" t="n">
         <v/>
       </c>
       <c r="K97" s="4" t="n">
-        <v>839.2</v>
+        <v>468.7</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>0.598</v>
+        <v>0.883</v>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>James Johnson; Sarah Lopez; Amanda Qureshi</t>
+          <t>David Fischer; Sophie Chen; Amanda Ueno; David Qureshi; Daniel Yamamoto</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -5280,81 +5260,19 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>Forge Bio</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>2027-07-13</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="n">
-        <v>1084.5</v>
-      </c>
-      <c r="H98" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I98" s="4" t="n">
-        <v>223.8</v>
-      </c>
-      <c r="J98" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K98" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="L98" s="4" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="M98" s="4" t="inlineStr">
-        <is>
-          <t>Andrew Yamamoto; Priya Mueller; Andrew Johnson; James Chen; Yuki Mueller</t>
-        </is>
-      </c>
-      <c r="N98" s="4" t="inlineStr">
-        <is>
-          <t>Fund IX</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>Fund IX Average</t>
         </is>
       </c>
-      <c r="G99" s="6" t="n">
-        <v>826.9</v>
-      </c>
-      <c r="H99" s="6" t="n">
-        <v>1411.5</v>
-      </c>
-      <c r="I99" s="6" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="J99" s="6" t="n">
-        <v>247.6</v>
-      </c>
-      <c r="K99" s="6" t="n">
-        <v>344.1</v>
+      <c r="G98" s="6" t="n">
+        <v>1369.8</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="K98" s="6" t="n">
+        <v>691.7</v>
       </c>
     </row>
   </sheetData>
